--- a/backtests/runs/Guangli_gpt4o/backtest_review_1409.xlsx
+++ b/backtests/runs/Guangli_gpt4o/backtest_review_1409.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://onedrive-global.kpmg.com/personal/weiliu3_kpmg_com_sg/Documents/Documents/Projects/Project X/CoCo AI Agent/CoCo_AI/backtests/runs/Guangli_gpt4o/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="11_36DD3F5CD167940E62355476585DCE3A8746DC86" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0480E0C-2E80-4575-A87F-3922B0B1B1C2}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="11_36DD3F5CD167940E62355476585DCE3A8746DC86" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{979FFF27-5C33-49BA-94A6-22F62C910093}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2760" yWindow="2620" windowWidth="14340" windowHeight="8200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1045,7 +1045,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="5" customFormat="1" ht="300" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" s="5" customFormat="1" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="5" customFormat="1" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" s="5" customFormat="1" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>15</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="300" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="300" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
@@ -1724,7 +1724,7 @@
   <autoFilter ref="A1:O21" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Guangli"/>
+        <filter val="YBR"/>
       </filters>
     </filterColumn>
     <filterColumn colId="13">
